--- a/NECP Scenario/Results/Regional Results/SERIFOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/SERIFOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.347289260345828E-08</v>
+        <v>4.930440932821622E-08</v>
       </c>
       <c r="C3">
-        <v>1.926402955092114E-08</v>
+        <v>2.836590307077932E-08</v>
       </c>
       <c r="D3">
-        <v>0.2107544927688403</v>
+        <v>0.2407869336451672</v>
       </c>
       <c r="E3">
-        <v>0.2158082185792346</v>
+        <v>0.2465058991305934</v>
       </c>
       <c r="F3">
-        <v>0.2408799198826035</v>
+        <v>0.2758762134311642</v>
       </c>
       <c r="G3">
-        <v>0.2656970551523946</v>
+        <v>0.3122102236808347</v>
       </c>
       <c r="H3">
-        <v>0.3064952820405478</v>
+        <v>0.3550256978470563</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.845195871516139E-08</v>
+        <v>4.190874793078386E-08</v>
       </c>
       <c r="C4">
-        <v>1.637442512050481E-08</v>
+        <v>2.411101761196247E-08</v>
       </c>
       <c r="D4">
-        <v>0.1791413188533697</v>
+        <v>0.2046688935983809</v>
       </c>
       <c r="E4">
-        <v>0.1834369857916614</v>
+        <v>0.2095300142610032</v>
       </c>
       <c r="F4">
-        <v>0.204747931900122</v>
+        <v>0.2344947814165144</v>
       </c>
       <c r="G4">
-        <v>0.2258424968795942</v>
+        <v>0.2653786901286856</v>
       </c>
       <c r="H4">
-        <v>0.260520989734442</v>
+        <v>0.3017718431699926</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.008824027902623028</v>
+        <v>0.008824029015324445</v>
       </c>
       <c r="C14">
-        <v>0.01001689722447443</v>
+        <v>0.01001689771564596</v>
       </c>
       <c r="D14">
-        <v>0.008832495184897413</v>
+        <v>0.00883248678372071</v>
       </c>
       <c r="E14">
-        <v>0.01047770454324675</v>
+        <v>0.01013652147274366</v>
       </c>
       <c r="F14">
-        <v>0.01270969129289536</v>
+        <v>0.01270971439864858</v>
       </c>
       <c r="G14">
-        <v>0.01564497578818581</v>
+        <v>0.01564501335779451</v>
       </c>
       <c r="H14">
-        <v>0.02046286727555779</v>
+        <v>0.02046308025487313</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.03081736685470675</v>
+        <v>0.03081738335125721</v>
       </c>
       <c r="C28">
-        <v>0.03510194625294427</v>
+        <v>0.03510195464433559</v>
       </c>
       <c r="D28">
-        <v>3.097707228888473E-08</v>
+        <v>4.586935839758326E-08</v>
       </c>
       <c r="E28">
-        <v>3.93944788371401E-08</v>
+        <v>5.823890911672542E-08</v>
       </c>
       <c r="F28">
-        <v>4.089097739560372E-08</v>
+        <v>6.029985229838073E-08</v>
       </c>
       <c r="G28">
-        <v>0.0001436621423152075</v>
+        <v>0.000143684829634059</v>
       </c>
       <c r="H28">
-        <v>0.0001725959791142156</v>
+        <v>0.0001727196415601757</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.008754933755679779</v>
+        <v>0.00875493843749945</v>
       </c>
       <c r="C29">
-        <v>0.009972143816701215</v>
+        <v>0.009972146198158244</v>
       </c>
       <c r="D29">
-        <v>8.792714897734671E-09</v>
+        <v>1.301985972263027E-08</v>
       </c>
       <c r="E29">
-        <v>1.118045632184765E-08</v>
+        <v>1.652867093606713E-08</v>
       </c>
       <c r="F29">
-        <v>1.160035092927016E-08</v>
+        <v>1.710642100758019E-08</v>
       </c>
       <c r="G29">
-        <v>4.081308449487268E-05</v>
+        <v>4.081951826932228E-05</v>
       </c>
       <c r="H29">
-        <v>4.903280231880958E-05</v>
+        <v>4.90678640773654E-05</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.04375637873659851</v>
+        <v>0.05048775780090289</v>
       </c>
       <c r="E30">
-        <v>0.05982156199829894</v>
+        <v>0.05982093536732205</v>
       </c>
       <c r="F30">
-        <v>0.05982085562994634</v>
+        <v>0.05981990057799458</v>
       </c>
       <c r="G30">
-        <v>0.05981990486961472</v>
+        <v>0.05981859487810282</v>
       </c>
       <c r="H30">
-        <v>0.05980677015680166</v>
+        <v>0.05979970383259031</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.0002491814044496785</v>
+        <v>0.0002491802492240664</v>
       </c>
       <c r="C31">
-        <v>0.000249182789367624</v>
+        <v>0.0002491822829932069</v>
       </c>
       <c r="D31">
-        <v>0.0002485024428151075</v>
+        <v>0.0002482845052458776</v>
       </c>
       <c r="E31">
-        <v>0.0002481565959383586</v>
+        <v>0.0002477881057799805</v>
       </c>
       <c r="F31">
-        <v>0.0002476007878666362</v>
+        <v>0.0002470894052880604</v>
       </c>
       <c r="G31">
-        <v>0.0002469041641053844</v>
+        <v>0.0002462787068489118</v>
       </c>
       <c r="H31">
-        <v>0.000239515580331168</v>
+        <v>0.0002376880478965393</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0.002226970563680159</v>
+        <v>0.002227046014483081</v>
       </c>
       <c r="E32">
-        <v>0.00277413775643331</v>
+        <v>0.003128712943986692</v>
       </c>
       <c r="F32">
-        <v>0.003379615310973775</v>
+        <v>0.003379636846995098</v>
       </c>
       <c r="G32">
-        <v>0.003451414319098131</v>
+        <v>0.003451412965348824</v>
       </c>
       <c r="H32">
-        <v>0.003483503807096664</v>
+        <v>0.003483392506159325</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.0003322428232565442</v>
+        <v>0.0003322417269890156</v>
       </c>
       <c r="C33">
-        <v>0.0003322441276079064</v>
+        <v>0.000332243645029406</v>
       </c>
       <c r="D33">
-        <v>0.000309752268930274</v>
+        <v>0.0003096852320044148</v>
       </c>
       <c r="E33">
-        <v>0.0003059038101420008</v>
+        <v>0.0002925117117532038</v>
       </c>
       <c r="F33">
-        <v>0.0003061073453159414</v>
+        <v>0.0003060627309519613</v>
       </c>
       <c r="G33">
-        <v>0.0003221601476875892</v>
+        <v>0.0003221239720916991</v>
       </c>
       <c r="H33">
-        <v>0.000331453749639913</v>
+        <v>0.0003313523150928874</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.6864370997543228</v>
+        <v>0.6559096038766538</v>
       </c>
       <c r="E36">
-        <v>0.696856215083098</v>
+        <v>0.68257485652107</v>
       </c>
       <c r="F36">
-        <v>0.6893253395332913</v>
+        <v>0.6701759947329751</v>
       </c>
       <c r="G36">
-        <v>0.6909585592497086</v>
+        <v>0.6664788785732786</v>
       </c>
       <c r="H36">
-        <v>0.7005157467076593</v>
+        <v>0.6732718021686046</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4.774509313445581E-09</v>
+        <v>7.026002442393288E-09</v>
       </c>
       <c r="C38">
-        <v>2.085239991664706E-09</v>
+        <v>3.07419289916748E-09</v>
       </c>
       <c r="D38">
-        <v>0.1141566894645048</v>
+        <v>0.1154730914468401</v>
       </c>
       <c r="E38">
-        <v>0.1269750819757152</v>
+        <v>0.13885252964629</v>
       </c>
       <c r="F38">
-        <v>0.1535085999381677</v>
+        <v>0.1757998874013801</v>
       </c>
       <c r="G38">
-        <v>0.1517891800515449</v>
+        <v>0.179411289689912</v>
       </c>
       <c r="H38">
-        <v>0.1422111405275412</v>
+        <v>0.1726046493888299</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.347289260345828E-08</v>
+        <v>4.930440932821622E-08</v>
       </c>
       <c r="C40">
-        <v>1.926402955092114E-08</v>
+        <v>2.836590307077932E-08</v>
       </c>
       <c r="D40">
-        <v>0.2107544927688403</v>
+        <v>0.2407869336451672</v>
       </c>
       <c r="E40">
-        <v>0.2158082185792346</v>
+        <v>0.2465058991305934</v>
       </c>
       <c r="F40">
-        <v>0.2408799198826035</v>
+        <v>0.2758762134311642</v>
       </c>
       <c r="G40">
-        <v>0.2656970551523946</v>
+        <v>0.3122102236808347</v>
       </c>
       <c r="H40">
-        <v>0.3064952820405478</v>
+        <v>0.3550256978470563</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2.845195871516139E-08</v>
+        <v>4.190874793078386E-08</v>
       </c>
       <c r="C41">
-        <v>1.637442512050481E-08</v>
+        <v>2.411101761196247E-08</v>
       </c>
       <c r="D41">
-        <v>0.1791413188533697</v>
+        <v>0.2046688935983809</v>
       </c>
       <c r="E41">
-        <v>0.1834369857916614</v>
+        <v>0.2095300142610032</v>
       </c>
       <c r="F41">
-        <v>0.204747931900122</v>
+        <v>0.2344947814165144</v>
       </c>
       <c r="G41">
-        <v>0.2258424968795942</v>
+        <v>0.2653786901286856</v>
       </c>
       <c r="H41">
-        <v>0.260520989734442</v>
+        <v>0.3017718431699926</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.020933888296893E-09</v>
+        <v>-7.395661397432369E-09</v>
       </c>
       <c r="C42">
-        <v>-2.889604430416325E-09</v>
+        <v>-4.254885458816853E-09</v>
       </c>
       <c r="D42">
-        <v>-0.03161317391547067</v>
+        <v>-0.03611804004678631</v>
       </c>
       <c r="E42">
-        <v>-0.03237123278757317</v>
+        <v>-0.03697588486959016</v>
       </c>
       <c r="F42">
-        <v>-0.03613198798248146</v>
+        <v>-0.04138143201464978</v>
       </c>
       <c r="G42">
-        <v>-0.03985455827280035</v>
+        <v>-0.04683153355214914</v>
       </c>
       <c r="H42">
-        <v>-0.04597429230610578</v>
+        <v>-0.05325385467706378</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1609,19 +1609,19 @@
         <v>-0</v>
       </c>
       <c r="D43">
-        <v>-0.6898160655959438</v>
+        <v>-0.6615148775006368</v>
       </c>
       <c r="E43">
-        <v>-0.7138631767830134</v>
+        <v>-0.6953243223376567</v>
       </c>
       <c r="F43">
-        <v>-0.7002927467638834</v>
+        <v>-0.6758924733977827</v>
       </c>
       <c r="G43">
-        <v>-0.6952473620023811</v>
+        <v>-0.6637887386549407</v>
       </c>
       <c r="H43">
-        <v>-0.6937562956172258</v>
+        <v>-0.6592237123423426</v>
       </c>
     </row>
     <row r="44" spans="1:8">
